--- a/relevancy_rating_parsed_Colorado.xlsx
+++ b/relevancy_rating_parsed_Colorado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D998"/>
+  <dimension ref="A1:D1320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17186,10 +17186,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D838" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D838" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="839">
@@ -17208,10 +17206,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D839" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="840">
@@ -17230,10 +17226,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D840" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="841">
@@ -17252,10 +17246,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D841" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="842">
@@ -17274,10 +17266,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D842" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="843">
@@ -17296,10 +17286,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D843" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="844">
@@ -17318,10 +17306,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D844" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="845">
@@ -17340,10 +17326,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D845" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="846">
@@ -17362,10 +17346,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D846" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="847">
@@ -17384,10 +17366,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D847" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="848">
@@ -17406,10 +17386,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D848" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="849">
@@ -17428,10 +17406,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D849" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="850">
@@ -17450,10 +17426,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D850" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="851">
@@ -17472,10 +17446,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D851" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="852">
@@ -17494,10 +17466,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D852" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="853">
@@ -17516,10 +17486,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D853" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="854">
@@ -17538,10 +17506,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D854" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="855">
@@ -17560,10 +17526,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D855" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D855" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="856">
@@ -17582,10 +17546,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D856" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="857">
@@ -17604,10 +17566,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D857" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="858">
@@ -17626,10 +17586,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D858" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="859">
@@ -17648,10 +17606,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D859" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="860">
@@ -17670,10 +17626,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D860" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="861">
@@ -17692,10 +17646,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D861" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D861" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="862">
@@ -17714,10 +17666,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D862" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="863">
@@ -17736,10 +17686,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D863" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D863" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="864">
@@ -17758,10 +17706,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D864" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="865">
@@ -17780,10 +17726,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D865" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D865" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="866">
@@ -17802,10 +17746,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D866" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="867">
@@ -17824,10 +17766,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D867" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="868">
@@ -17846,10 +17786,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D868" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="869">
@@ -17868,10 +17806,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D869" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D869" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="870">
@@ -17890,10 +17826,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D870" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="871">
@@ -17912,10 +17846,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D871" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="872">
@@ -17934,10 +17866,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D872" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="873">
@@ -17956,10 +17886,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D873" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D873" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="874">
@@ -17978,10 +17906,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D874" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="875">
@@ -18000,10 +17926,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D875" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="876">
@@ -18022,10 +17946,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D876" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="877">
@@ -18044,10 +17966,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D877" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="878">
@@ -18066,10 +17986,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D878" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="879">
@@ -18088,10 +18006,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D879" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="880">
@@ -18110,10 +18026,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D880" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="881">
@@ -18132,10 +18046,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D881" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="882">
@@ -18154,10 +18066,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D882" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="883">
@@ -18176,10 +18086,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D883" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D883" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="884">
@@ -18198,10 +18106,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D884" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="885">
@@ -18220,10 +18126,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D885" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="886">
@@ -18242,10 +18146,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D886" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="887">
@@ -18264,10 +18166,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D887" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="888">
@@ -18286,10 +18186,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D888" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="889">
@@ -18308,10 +18206,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D889" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D889" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="890">
@@ -18330,10 +18226,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D890" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D890" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="891">
@@ -18352,10 +18246,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D891" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="892">
@@ -18374,10 +18266,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D892" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D892" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="893">
@@ -18396,10 +18286,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D893" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D893" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="894">
@@ -18418,10 +18306,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D894" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D894" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="895">
@@ -18440,10 +18326,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D895" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D895" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="896">
@@ -18462,10 +18346,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D896" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D896" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="897">
@@ -18484,10 +18366,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D897" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D897" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="898">
@@ -18506,10 +18386,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D898" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D898" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="899">
@@ -18528,10 +18406,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D899" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="900">
@@ -18550,10 +18426,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D900" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="901">
@@ -18572,10 +18446,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D901" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D901" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="902">
@@ -18594,10 +18466,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D902" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D902" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="903">
@@ -18616,10 +18486,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D903" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D903" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="904">
@@ -18638,10 +18506,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D904" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D904" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="905">
@@ -18660,10 +18526,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D905" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D905" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="906">
@@ -18682,10 +18546,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D906" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D906" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="907">
@@ -18704,10 +18566,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D907" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D907" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="908">
@@ -18726,10 +18586,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D908" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D908" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="909">
@@ -18748,10 +18606,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D909" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D909" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="910">
@@ -18770,10 +18626,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D910" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D910" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="911">
@@ -18792,10 +18646,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D911" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="912">
@@ -18814,10 +18666,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D912" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D912" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="913">
@@ -18836,10 +18686,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D913" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D913" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="914">
@@ -18858,10 +18706,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D914" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D914" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="915">
@@ -18880,10 +18726,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D915" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D915" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="916">
@@ -18902,10 +18746,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D916" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D916" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="917">
@@ -18924,10 +18766,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D917" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D917" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="918">
@@ -18946,10 +18786,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D918" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D918" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="919">
@@ -18968,10 +18806,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D919" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D919" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="920">
@@ -18990,10 +18826,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D920" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D920" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="921">
@@ -19012,10 +18846,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D921" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D921" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="922">
@@ -19034,10 +18866,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D922" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D922" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="923">
@@ -19056,10 +18886,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D923" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D923" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="924">
@@ -19078,10 +18906,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D924" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D924" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="925">
@@ -19100,10 +18926,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D925" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D925" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="926">
@@ -19122,10 +18946,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D926" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D926" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="927">
@@ -19144,10 +18966,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D927" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D927" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="928">
@@ -19166,10 +18986,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D928" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D928" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="929">
@@ -19188,10 +19006,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D929" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D929" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="930">
@@ -19210,10 +19026,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D930" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D930" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="931">
@@ -19232,10 +19046,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D931" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D931" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="932">
@@ -19254,10 +19066,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D932" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D932" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="933">
@@ -19276,10 +19086,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D933" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D933" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="934">
@@ -19298,10 +19106,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D934" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D934" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="935">
@@ -19320,10 +19126,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D935" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D935" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="936">
@@ -19342,10 +19146,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D936" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D936" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="937">
@@ -19364,10 +19166,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D937" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D937" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="938">
@@ -19386,10 +19186,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D938" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D938" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="939">
@@ -19408,10 +19206,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D939" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D939" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="940">
@@ -19430,10 +19226,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D940" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D940" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="941">
@@ -19452,10 +19246,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D941" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D941" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="942">
@@ -19474,10 +19266,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D942" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D942" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="943">
@@ -19496,10 +19286,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D943" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D943" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="944">
@@ -19518,10 +19306,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D944" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D944" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="945">
@@ -19540,10 +19326,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D945" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D945" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="946">
@@ -19562,10 +19346,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D946" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D946" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="947">
@@ -19584,10 +19366,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D947" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D947" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="948">
@@ -19606,10 +19386,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D948" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D948" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="949">
@@ -19628,10 +19406,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D949" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D949" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="950">
@@ -19650,10 +19426,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D950" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D950" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="951">
@@ -19672,10 +19446,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D951" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D951" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="952">
@@ -19694,10 +19466,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D952" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D952" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="953">
@@ -19716,10 +19486,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D953" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D953" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="954">
@@ -19738,10 +19506,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D954" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D954" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="955">
@@ -19760,10 +19526,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D955" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D955" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="956">
@@ -19782,10 +19546,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D956" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D956" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="957">
@@ -19804,10 +19566,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D957" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D957" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="958">
@@ -19826,10 +19586,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D958" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D958" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="959">
@@ -19848,10 +19606,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D959" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D959" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="960">
@@ -19870,10 +19626,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D960" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D960" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="961">
@@ -19892,10 +19646,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D961" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D961" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="962">
@@ -19914,10 +19666,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D962" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D962" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="963">
@@ -19936,10 +19686,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D963" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D963" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="964">
@@ -19958,10 +19706,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D964" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D964" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="965">
@@ -19980,10 +19726,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D965" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D965" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="966">
@@ -20002,10 +19746,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D966" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D966" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="967">
@@ -20024,10 +19766,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D967" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D967" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="968">
@@ -20046,10 +19786,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D968" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D968" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="969">
@@ -20068,10 +19806,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D969" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D969" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="970">
@@ -20090,10 +19826,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D970" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D970" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="971">
@@ -20112,10 +19846,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D971" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D971" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="972">
@@ -20134,10 +19866,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D972" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D972" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="973">
@@ -20156,10 +19886,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D973" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D973" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="974">
@@ -20178,10 +19906,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D974" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D974" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="975">
@@ -20200,10 +19926,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D975" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D975" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="976">
@@ -20222,10 +19946,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D976" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D976" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="977">
@@ -20244,10 +19966,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D977" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D977" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="978">
@@ -20266,10 +19986,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D978" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D978" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="979">
@@ -20288,10 +20006,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D979" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D979" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="980">
@@ -20310,10 +20026,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D980" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D980" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="981">
@@ -20332,10 +20046,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D981" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D981" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="982">
@@ -20354,10 +20066,8 @@
           <t>6-1-1701</t>
         </is>
       </c>
-      <c r="D982" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D982" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="983">
@@ -20376,10 +20086,8 @@
           <t>6-1-1702</t>
         </is>
       </c>
-      <c r="D983" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D983" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="984">
@@ -20398,10 +20106,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D984" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D984" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="985">
@@ -20420,10 +20126,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D985" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D985" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="986">
@@ -20442,10 +20146,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D986" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D986" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="987">
@@ -20464,10 +20166,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D987" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D987" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="988">
@@ -20486,10 +20186,8 @@
           <t>6-1-1703</t>
         </is>
       </c>
-      <c r="D988" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D988" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="989">
@@ -20508,10 +20206,8 @@
           <t>6-1-1704</t>
         </is>
       </c>
-      <c r="D989" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D989" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="990">
@@ -20530,10 +20226,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D990" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D990" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="991">
@@ -20552,10 +20246,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D991" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D991" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="992">
@@ -20574,10 +20266,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D992" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D992" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="993">
@@ -20596,10 +20286,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D993" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D993" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="994">
@@ -20618,10 +20306,8 @@
           <t>6-1-1705</t>
         </is>
       </c>
-      <c r="D994" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D994" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="995">
@@ -20640,10 +20326,8 @@
           <t>6-1-1706</t>
         </is>
       </c>
-      <c r="D995" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D995" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="996">
@@ -20662,10 +20346,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D996" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D996" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="997">
@@ -20684,10 +20366,8 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D997" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D997" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="998">
@@ -20706,7 +20386,6767 @@
           <t>6-1-1707</t>
         </is>
       </c>
-      <c r="D998" t="inlineStr">
+      <c r="D998" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1028" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1029" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1030" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1031" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1032" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1033" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1034" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1035" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1036" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1037" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1038" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1039" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1040" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1041" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1042" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1043" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1044" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1045" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1046" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1047" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1048" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1049" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1050" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1051" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1052" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1053" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1054" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1055" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1056" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1057" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1058" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1059" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1060" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1061" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1062" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1063" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1064" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1065" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1066" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1067" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1068" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1069" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1070" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1071" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1072" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1073" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1074" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1075" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1076" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1077" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1078" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1079" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1080" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1081" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1082" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1083" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1084" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1085" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1086" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1087" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1088" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1089" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1090" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1091" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1092" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1093" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1094" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1114" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1115" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1116" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1117" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1119" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1121" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1123" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1124" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1126" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1128" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1136" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1137" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1138" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1147" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1149" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1157" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1158" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>mc7</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1159" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>System Name</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Versioning Information</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Primary Developer/Org</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Contact Info</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>System Overview</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Primary intended uses</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Primary intended users</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Out-of-scope use cases</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Terms and conditions</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Current legal compliance status</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Dataset Description</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Collection Method</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Bias Mitigation Measures</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Usage Constraints</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Summary of Performance Assessment</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Disaggregated Performance</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Testing Contexts</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Evaluations for Edge Cases or Adversarial Inputs</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Potential Risks and Harms</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Actions taken</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>6-1-1701</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>6-1-1702</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>6-1-1703</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>6-1-1704</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>6-1-1705</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>6-1-1706</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Misuse Scenarios</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Human Oversight</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>mc8</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>6-1-1707</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
         <is>
           <t>3</t>
         </is>
